--- a/XRF_list_Aug_2026.xlsx
+++ b/XRF_list_Aug_2026.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhang\Documents\GitHub\Andrews_CompostMulch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{049A2B2C-1085-434C-BAA9-337A2B64F55D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2F9F13A-6A7E-4A15-BC0C-B13197767103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{5C8F5324-6E1B-4FFE-BB11-C316667C42A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,17 +41,17 @@
     <t>Sample</t>
   </si>
   <si>
-    <t>Ideal_mass_g</t>
+    <t>Mass_g (+-0.1g)</t>
   </si>
   <si>
-    <t>Mass_g (+-0.1g)</t>
+    <t>Ideal_mass_g</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -446,272 +446,328 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2CD18B3-3D3D-48A2-A640-33733FD1CA54}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="1">
+        <v>2.0059999999999998</v>
+      </c>
       <c r="C2" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="1"/>
+      <c r="B3" s="1">
+        <v>2.0009000000000001</v>
+      </c>
       <c r="C3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="1"/>
+      <c r="B4" s="1">
+        <v>2.0049000000000001</v>
+      </c>
       <c r="C4" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="1"/>
+      <c r="B5" s="1">
+        <v>1.9993000000000001</v>
+      </c>
       <c r="C5" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="1"/>
+      <c r="B6" s="1">
+        <v>1.9978</v>
+      </c>
       <c r="C6" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="1"/>
+      <c r="B7" s="1">
+        <v>2.0091999999999999</v>
+      </c>
       <c r="C7" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="1"/>
+      <c r="B8" s="1">
+        <v>2.0026000000000002</v>
+      </c>
       <c r="C8" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="1"/>
+      <c r="B9" s="1">
+        <v>2.0028000000000001</v>
+      </c>
       <c r="C9" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="1"/>
+      <c r="B10" s="1">
+        <v>2.0084</v>
+      </c>
       <c r="C10" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="1"/>
+      <c r="B11" s="1">
+        <v>1.9943</v>
+      </c>
       <c r="C11" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="1"/>
+      <c r="B12" s="1">
+        <v>1.9928999999999999</v>
+      </c>
       <c r="C12" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="1"/>
+      <c r="B13" s="1">
+        <v>2.0051000000000001</v>
+      </c>
       <c r="C13" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="1"/>
+      <c r="B14" s="1">
+        <v>1.9992000000000001</v>
+      </c>
       <c r="C14" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="1"/>
+      <c r="B15" s="1">
+        <v>1.9994000000000001</v>
+      </c>
       <c r="C15" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="1"/>
+      <c r="B16" s="1">
+        <v>2.0059</v>
+      </c>
       <c r="C16" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="1"/>
+      <c r="B17" s="1">
+        <v>2.0062000000000002</v>
+      </c>
       <c r="C17" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="1"/>
+      <c r="B18" s="1">
+        <v>2.0070000000000001</v>
+      </c>
       <c r="C18" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="1"/>
+      <c r="B19" s="1">
+        <v>1.9938</v>
+      </c>
       <c r="C19" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="1"/>
+      <c r="B20" s="1">
+        <v>1.9963</v>
+      </c>
       <c r="C20" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="1"/>
+      <c r="B21" s="1">
+        <v>1.9922</v>
+      </c>
       <c r="C21" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="1"/>
+      <c r="B22" s="1">
+        <v>2.008</v>
+      </c>
       <c r="C22" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" s="1"/>
+      <c r="B23" s="1">
+        <v>2.0089000000000001</v>
+      </c>
       <c r="C23" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="1"/>
+      <c r="B24" s="1">
+        <v>1.9939</v>
+      </c>
       <c r="C24" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" s="1"/>
+      <c r="B25" s="1">
+        <v>2.0068000000000001</v>
+      </c>
       <c r="C25" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" s="1"/>
+      <c r="B26" s="1">
+        <v>2.0022000000000002</v>
+      </c>
       <c r="C26" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" s="1"/>
+      <c r="B27" s="1">
+        <v>1.9954000000000001</v>
+      </c>
       <c r="C27" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="B28" s="1"/>
+      <c r="B28" s="1">
+        <v>1.9958</v>
+      </c>
       <c r="C28" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="B29" s="1"/>
+      <c r="B29" s="1">
+        <v>1.9936</v>
+      </c>
       <c r="C29" s="1">
         <v>2</v>
       </c>
